--- a/out/Attention-mamba2_repeat_4_000008.xlsx
+++ b/out/Attention-mamba2_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.2927231521932764</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001248362669547787</v>
+        <v>-7.963731762464158e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1434128937158519</v>
+        <v>-0.09148798219401852</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.088844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.09156761951164319</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.143659862293859</v>
+        <v>-0.09163800591905182</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4391597193108276</v>
+        <v>0.2530934911980691</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7355032935492368</v>
+        <v>0.4150349252481531</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03129003779671281</v>
+        <v>0.01803285810938519</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3582187484573354</v>
+        <v>0.1976011605290549</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05487206511891909</v>
+        <v>0.03162336062868121</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4366625824287161</v>
+        <v>0.2428092626329469</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06666307878002239</v>
+        <v>0.03841896026112867</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5151118212486583</v>
+        <v>0.2880205568831893</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01764088591484346</v>
+        <v>0.01016583069642506</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4836447788281816</v>
+        <v>0.2698851613265211</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009800036326149857</v>
+        <v>0.00564593820742671</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4855877303631394</v>
+        <v>0.271002803377555</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02059114417801685</v>
+        <v>0.01186542279913992</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5169835926099599</v>
+        <v>0.2890954051100633</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008087393957669472</v>
+        <v>0.004658844527235129</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5125477620272166</v>
+        <v>0.2865368090947766</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005758008286614136</v>
+        <v>0.003315500135208684</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5159730128014008</v>
+        <v>0.2885087476204461</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002262678302072143</v>
+        <v>0.001302649224488308</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5147372346819269</v>
+        <v>0.2877942353802803</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001282079994452907</v>
+        <v>0.0007364197333315546</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5150375787173296</v>
+        <v>0.2879652060699321</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004858863384249597</v>
+        <v>0.0002780229845942949</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5147246998374905</v>
+        <v>0.287782696955001</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.00022510073267398</v>
+        <v>0.0001271152532099407</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.2927231521932764</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5146886657872706</v>
+        <v>0.2877598048645896</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.896183061281334e-05</v>
+        <v>4.343951766123847e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.2927231521932764</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5146221035902642</v>
+        <v>0.28771916383296</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.980325908626812e-05</v>
+        <v>9.309572549770066e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5145823375441054</v>
+        <v>0.2876939665716879</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.401629543134059e-06</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5145773181834123</v>
+        <v>0.2876889554020574</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5145733001390687</v>
+        <v>0.2876845370680047</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5145708654688779</v>
+        <v>0.2876810029707528</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5145653482268882</v>
+        <v>0.2876757071407486</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5145590242328802</v>
+        <v>0.2876700451437449</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5145536564443018</v>
+        <v>0.2876698614012858</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5145536931927935</v>
+        <v>0.2876698981497774</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5145538034382691</v>
+        <v>0.287670008395253</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5145538769352527</v>
+        <v>0.2876700818922366</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5145540606777118</v>
+        <v>0.2876702656346958</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5145556041143683</v>
+        <v>0.2876718090713523</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.688844415955533</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5145570740540414</v>
+        <v>0.2876732790110254</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.688844415955533</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5145583235027634</v>
+        <v>0.2876745284597473</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.2927231521932764</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5145596831969608</v>
+        <v>0.2876758881539446</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.2927231521932764</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5145574782874515</v>
+        <v>0.2876736832444354</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5145570740540414</v>
+        <v>0.2876732790110254</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5145562288387294</v>
+        <v>0.2876724337957133</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5145567800661067</v>
+        <v>0.2876729850230906</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5145564493296803</v>
+        <v>0.2876726542866642</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5145561553417458</v>
+        <v>0.2876723602987297</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5145562288387294</v>
+        <v>0.2876724337957133</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.688844415955533</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5145557878568275</v>
+        <v>0.2876719928138114</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.688844415955533</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5145556776113519</v>
+        <v>0.2876718825683359</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.111245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5145556408628602</v>
+        <v>0.2876718458198442</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.111245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5145557878568275</v>
+        <v>0.2876719928138114</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5145553101264339</v>
+        <v>0.2876715150834178</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5145562655872211</v>
+        <v>0.287672470544205</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5145562288387294</v>
+        <v>0.2876724337957133</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5145558981023031</v>
+        <v>0.287672103059287</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.514556339084205</v>
+        <v>0.2876725440411889</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5145557143598438</v>
+        <v>0.2876719193168278</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5145555306173847</v>
+        <v>0.2876717355743686</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.711245132341913</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5145551263839747</v>
+        <v>0.2876713313409586</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5145542811686628</v>
+        <v>0.2876704861256466</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5145542444201711</v>
+        <v>0.2876704493771549</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5145543914141383</v>
+        <v>0.2876705963711222</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5145543179171547</v>
+        <v>0.2876705228741385</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5145543914141383</v>
+        <v>0.2876705963711222</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5145544281626302</v>
+        <v>0.2876706331196141</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5145543179171547</v>
+        <v>0.2876705228741385</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5145547588990566</v>
+        <v>0.2876709638560405</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.514554648653581</v>
+        <v>0.2876708536105649</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5145546119050891</v>
+        <v>0.287670816862073</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5145545384081055</v>
+        <v>0.2876707433650894</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5145545016596138</v>
+        <v>0.2876707066165977</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5145542811686628</v>
+        <v>0.2876704861256466</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5145542076716791</v>
+        <v>0.287670412628663</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5145541341746954</v>
+        <v>0.2876703391316794</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5145541709231874</v>
+        <v>0.2876703758801713</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5145540606777118</v>
+        <v>0.2876702656346958</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5145541709231874</v>
+        <v>0.2876703758801713</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5145544649111219</v>
+        <v>0.2876706698681058</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000008.xlsx
+++ b/out/Attention-mamba2_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.3676904797093241</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.088844415955533</v>
+        <v>0.2723299884729494</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.088844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001248362669547787</v>
+        <v>-0.00012081046412664</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1434128937158519</v>
+        <v>-0.138788019492925</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.088844415955533</v>
+        <v>0.9123504566552229</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.088844415955533</v>
+        <v>0.2723299884729494</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.3676904797093241</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.688844415955533</v>
+        <v>0.4723299884729494</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1435377299828067</v>
+        <v>-0.1389088299570517</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.688844415955533</v>
+        <v>0.4723299884729494</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.143659862293859</v>
+        <v>-0.1390051985261299</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4391597193108276</v>
+        <v>0.3465194273690277</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7355032935492368</v>
+        <v>0.5546989862015809</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03129003779671281</v>
+        <v>0.02468943644623744</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8077109478915975</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3582187484573354</v>
+        <v>0.2570025765290412</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05487206511891909</v>
+        <v>0.04329685931442628</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4366625824287161</v>
+        <v>0.3188986192733969</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06666307878002239</v>
+        <v>0.05260025896198708</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5151118212486583</v>
+        <v>0.3807987823125292</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01764088591484346</v>
+        <v>0.01391951144426604</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.3676904797093241</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4836447788281816</v>
+        <v>0.3559697652663681</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009800036326149857</v>
+        <v>0.00773160877220116</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.3676904797093241</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4855877303631394</v>
+        <v>0.3575017932225601</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02059114417801685</v>
+        <v>0.01624732651448101</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5169835926099599</v>
+        <v>0.3822747698399683</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008087393957669472</v>
+        <v>0.006379780147386029</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.111245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5125477620272166</v>
+        <v>0.3787735787575044</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005758008286614136</v>
+        <v>0.004541929016316931</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5159730128014008</v>
+        <v>0.3814755107882456</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002262678302072143</v>
+        <v>0.001784700600078494</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5147372346819269</v>
+        <v>0.3804990767067142</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001282079994452907</v>
+        <v>0.00101079127705924</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5150375787173296</v>
+        <v>0.3807350995306699</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004858863384249597</v>
+        <v>0.0003825418461249682</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.3676904797093241</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5147246998374905</v>
+        <v>0.3804870372571128</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.00022510073267398</v>
+        <v>0.0001766584731636684</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5146886657872706</v>
+        <v>0.3804575366911497</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.896183061281334e-05</v>
+        <v>6.12006741370259e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5146221035902642</v>
+        <v>0.3804039350768318</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.980325908626812e-05</v>
+        <v>1.455641581801909e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8077109478915975</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5145823375441054</v>
+        <v>0.3803714534231166</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.401629543134059e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5145773181834123</v>
+        <v>0.3803664377856338</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.3676904797093241</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5145733001390687</v>
+        <v>0.3803622016165599</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.688844415955533</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5145708654688779</v>
+        <v>0.3803592177374542</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5145653482268882</v>
+        <v>0.3803537739924479</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8077109478915975</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5145590242328802</v>
+        <v>0.3803477812590175</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5145536564443018</v>
+        <v>0.3803424134704391</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5145536931927935</v>
+        <v>0.3803424502189308</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5145538034382691</v>
+        <v>0.3803425604644064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5145538769352527</v>
+        <v>0.38034263396139</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5145540606777118</v>
+        <v>0.3803428177038491</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.3676904797093241</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5145556041143683</v>
+        <v>0.3803443611405056</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.688844415955533</v>
+        <v>0.4723299884729494</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5145570740540414</v>
+        <v>0.3803458310801787</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5145583235027634</v>
+        <v>0.3803470805289007</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.688844415955533</v>
+        <v>0.4723299884729496</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5145596831969608</v>
+        <v>0.380348440223098</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5145574782874515</v>
+        <v>0.3803462353135887</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8077109478915975</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5145570740540414</v>
+        <v>0.3803458310801787</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5145562288387294</v>
+        <v>0.3803449858648668</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5145567800661067</v>
+        <v>0.380345537092244</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5145564493296803</v>
+        <v>0.3803452063558176</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5145561553417458</v>
+        <v>0.3803449123678831</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.3676904797093241</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5145562288387294</v>
+        <v>0.3803449858648668</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.688844415955533</v>
+        <v>0.4723299884729494</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5145557878568275</v>
+        <v>0.3803445448829648</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.688844415955533</v>
+        <v>0.4723299884729494</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5145556776113519</v>
+        <v>0.3803444346374892</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5145556408628602</v>
+        <v>0.3803443978889975</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.111245132341913</v>
+        <v>-0.8077109478915975</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5145557878568275</v>
+        <v>0.3803445448829648</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5145553101264339</v>
+        <v>0.3803440671525712</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5145562655872211</v>
+        <v>0.3803450226133585</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5145562288387294</v>
+        <v>0.3803449858648668</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5145558981023031</v>
+        <v>0.3803446551284403</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.514556339084205</v>
+        <v>0.3803450961103423</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5145557143598438</v>
+        <v>0.3803444713859812</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5145555306173847</v>
+        <v>0.380344287643522</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5145551263839747</v>
+        <v>0.380343883410112</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5145542811686628</v>
+        <v>0.3803430381948</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5145542444201711</v>
+        <v>0.3803430014463083</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5145543914141383</v>
+        <v>0.3803431484402756</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5145543179171547</v>
+        <v>0.3803430749432919</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5145543914141383</v>
+        <v>0.3803431484402756</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5145544281626302</v>
+        <v>0.3803431851887675</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.167690479709324</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5145543179171547</v>
+        <v>0.3803430749432919</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.688844415955533</v>
+        <v>0.4723299884729494</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5145547588990566</v>
+        <v>0.3803435159251939</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.514554648653581</v>
+        <v>0.3803434056797184</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5145546119050891</v>
+        <v>0.3803433689312264</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5145545384081055</v>
+        <v>0.3803432954342428</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5145545016596138</v>
+        <v>0.3803432586857511</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5145542811686628</v>
+        <v>0.3803430381948</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5145542076716791</v>
+        <v>0.3803429646978164</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.688844415955533</v>
+        <v>1.112350456655223</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5145541341746954</v>
+        <v>0.3803428912008328</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.688844415955533</v>
+        <v>0.4723299884729496</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5145541709231874</v>
+        <v>0.3803429279493247</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.711245132341913</v>
+        <v>-0.367690479709324</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5145540606777118</v>
+        <v>0.3803428177038491</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5145541709231874</v>
+        <v>0.3803429279493247</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.711245132341913</v>
+        <v>-1.007710947891598</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5145544649111219</v>
+        <v>0.3803432219372592</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000008.xlsx
+++ b/out/Attention-mamba2_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1886498481035233</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.08013425767421722</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3676904797093241</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.04162902757525444</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2723299884729494</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.04505695030093193</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.112350456655223</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.04745703563094139</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.112350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.04942620918154716</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.112350456655223</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.03486614301800728</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.112350456655223</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01855827122926712</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.112350456655223</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.02233317866921425</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.112350456655223</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01893867924809456</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.112350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01991397142410278</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.112350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01978090405464172</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.112350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01609185710549355</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.02158470451831818</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0581112913787365</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.03345482051372528</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.007433459162712097</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.008193608373403549</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01120477914810181</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0102761834859848</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01146946474909782</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01238514110445976</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01365263760089874</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01807137206196785</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01877370476722717</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01339970901608467</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01443076878786087</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0145423598587513</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01735229417681694</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.03710253164172173</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0943184494972229</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.05377599969506264</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02886604890227318</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.02165120840072632</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.02096755057573318</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02378822863101959</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01362145319581032</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01371388509869576</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.04040211066603661</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.05428392067551613</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.05079007521271706</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.1087712645530701</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.08984789252281189</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01665005460381508</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.9123504566552229</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.00012081046412664</v>
+        <v>-0.0001068428702487145</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.138788019492925</v>
+        <v>-0.1227419368510789</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.002765312790870667</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.9123504566552229</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02655012160539627</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2723299884729494</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0174997765570879</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3676904797093241</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.008960533887147903</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01854705810546875</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01891398802399635</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.03107882291078568</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01529546175152063</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.03105530142784119</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01801592670381069</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0302362497895956</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0233248844742775</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.167690479709324</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01194847002625465</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4723299884729494</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1389088299570517</v>
+        <v>-0.1228487797213277</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01881054788827896</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4723299884729494</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1390051985261299</v>
+        <v>-0.1229307420869987</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3465194273690277</v>
+        <v>0.294717744047626</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.1827272474765778</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.167690479709324</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5546989862015809</v>
+        <v>0.4670711293479043</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02468943644623744</v>
+        <v>0.02099861397192334</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.053975909948349</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8077109478915975</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2570025765290412</v>
+        <v>0.213877339317356</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04329685931442628</v>
+        <v>0.03682441423562201</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.04847016185522079</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3188986192733969</v>
+        <v>0.2665205460915822</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05260025896198708</v>
+        <v>0.04473700258093773</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.1073919832706451</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3807987823125292</v>
+        <v>0.3191672573040025</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01391951144426604</v>
+        <v>0.01183869679040025</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.04729883745312691</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3676904797093241</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3559697652663681</v>
+        <v>0.29804990662757</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00773160877220116</v>
+        <v>0.006575226429163506</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.03915832564234734</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3676904797093241</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3575017932225601</v>
+        <v>0.2993521654620404</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01624732651448101</v>
+        <v>0.01381839328174092</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.1650967001914978</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.167690479709324</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3822747698399683</v>
+        <v>0.3204208891864845</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006379780147386029</v>
+        <v>0.005425454131426205</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.1216093003749847</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3787735787575044</v>
+        <v>0.3174425512138684</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004541929016316931</v>
+        <v>0.003862304573058633</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.05516818910837173</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3814755107882456</v>
+        <v>0.3197394435322525</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001784700600078494</v>
+        <v>0.001517196033905912</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.06412202119827271</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.007710947891598</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3804990767067142</v>
+        <v>0.3189085211841464</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.00101079127705924</v>
+        <v>0.0008581913735253026</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02081144228577614</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.007710947891598</v>
+        <v>0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3807350995306699</v>
+        <v>0.3191083633266634</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003825418461249682</v>
+        <v>0.0003238233845908821</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.001222426071763039</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3676904797093241</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3804870372571128</v>
+        <v>0.3188967611853937</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001766584731636684</v>
+        <v>0.0001491344620782641</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01230823993682861</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.167690479709324</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3804575366911497</v>
+        <v>0.3188708993294109</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.12006741370259e-05</v>
+        <v>5.151277060477821e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0295029878616333</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.167690479709324</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3804039350768318</v>
+        <v>0.318824367123832</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.455641581801909e-05</v>
+        <v>1.169450130806508e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02844896167516708</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8077109478915975</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3803714534231166</v>
+        <v>0.3187958587750858</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0242574792355299</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.007710947891598</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3803664377856338</v>
+        <v>0.3187908453715292</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.001329738646745682</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3676904797093241</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3803622016165599</v>
+        <v>0.3187864997457198</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.04324937984347343</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.167690479709324</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3803592177374542</v>
+        <v>0.3187831493909271</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003571359440684319</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.167690479709324</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3803537739924479</v>
+        <v>0.3187777800639393</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.04930078610777855</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8077109478915975</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3803477812590175</v>
+        <v>0.3187717873305089</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.07249122112989426</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3803424134704391</v>
+        <v>0.3187664195419305</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.1613975018262863</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3803424502189308</v>
+        <v>0.3187664562904222</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02064279839396477</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3803425604644064</v>
+        <v>0.3187665665358978</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003574509173631668</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.38034263396139</v>
+        <v>0.3187666400328814</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.05989629775285721</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3803428177038491</v>
+        <v>0.3187668237753405</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.06548794358968735</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3676904797093241</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3803443611405056</v>
+        <v>0.318768367211997</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0782000869512558</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4723299884729494</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3803458310801787</v>
+        <v>0.3187698371516701</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.04803705587983131</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.112350456655223</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3803470805289007</v>
+        <v>0.3187710866003921</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0493554063141346</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4723299884729496</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.380348440223098</v>
+        <v>0.3187724462945895</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.1342747360467911</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.167690479709324</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3803462353135887</v>
+        <v>0.3187702413850801</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.1668742746114731</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8077109478915975</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3803458310801787</v>
+        <v>0.3187698371516701</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.1246128529310226</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3803449858648668</v>
+        <v>0.3187689919363582</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.03340354561805725</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.380345537092244</v>
+        <v>0.3187695431637354</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.0190462488681078</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3803452063558176</v>
+        <v>0.318769212427309</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02656613290309906</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.007710947891598</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3803449123678831</v>
+        <v>0.3187689184393745</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0183498952537775</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3676904797093241</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3803449858648668</v>
+        <v>0.3187689919363582</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.02306080982089043</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.4723299884729494</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3803445448829648</v>
+        <v>0.3187685509544562</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01138744130730629</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4723299884729494</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3803444346374892</v>
+        <v>0.3187684407089806</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.001458439975976944</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.167690479709324</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3803443978889975</v>
+        <v>0.3187684039604889</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.03451543301343918</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8077109478915975</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3803445448829648</v>
+        <v>0.3187685509544562</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.1470412611961365</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3803440671525712</v>
+        <v>0.3187680732240626</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.1570199429988861</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3803450226133585</v>
+        <v>0.3187690286848499</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.05175910890102386</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3803449858648668</v>
+        <v>0.3187689919363582</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01836398802697659</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3803446551284403</v>
+        <v>0.3187686611999317</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01135395839810371</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3803450961103423</v>
+        <v>0.3187691021818337</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.02110322192311287</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.007710947891598</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3803444713859812</v>
+        <v>0.3187684774574726</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.03274764120578766</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.007710947891598</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.380344287643522</v>
+        <v>0.3187682937150134</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.07959772646427155</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.007710947891598</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.380343883410112</v>
+        <v>0.3187678894816034</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.06955255568027496</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.007710947891598</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3803430381948</v>
+        <v>0.3187670442662914</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.03745122626423836</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3803430014463083</v>
+        <v>0.3187670075177997</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.06809353828430176</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3803431484402756</v>
+        <v>0.318767154511767</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.04410015791654587</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3803430749432919</v>
+        <v>0.3187670810147833</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.1411798596382141</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3803431484402756</v>
+        <v>0.318767154511767</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.05183438956737518</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3803431851887675</v>
+        <v>0.3187671912602589</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.08213810622692108</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.167690479709324</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3803430749432919</v>
+        <v>0.3187670810147833</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01046323776245117</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4723299884729494</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3803435159251939</v>
+        <v>0.3187675219966853</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.01544813439249992</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.112350456655223</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3803434056797184</v>
+        <v>0.3187674117512098</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.03413337096571922</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.112350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3803433689312264</v>
+        <v>0.3187673750027178</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01688258722424507</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.112350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3803432954342428</v>
+        <v>0.3187673015057342</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.03928621485829353</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.112350456655223</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3803432586857511</v>
+        <v>0.3187672647572425</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.02885832265019417</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.112350456655223</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3803430381948</v>
+        <v>0.3187670442662914</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.00938604399561882</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.112350456655223</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3803429646978164</v>
+        <v>0.3187669707693078</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.03358450531959534</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.112350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3803428912008328</v>
+        <v>0.3187668972723242</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01468846574425697</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.4723299884729496</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3803429279493247</v>
+        <v>0.3187669340208161</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.04859092831611633</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.367690479709324</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3803428177038491</v>
+        <v>0.3187668237753405</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.1234141886234283</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.007710947891598</v>
+        <v>-0.9299999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3803429279493247</v>
+        <v>0.3187669340208161</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.04557560384273529</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.007710947891598</v>
+        <v>-1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3803432219372592</v>
+        <v>0.3187672280087506</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000008.xlsx
+++ b/out/Attention-mamba2_repeat_4_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1886498481035233</v>
+        <v>-0.1856022477149963</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.08013425767421722</v>
+        <v>-0.07828117161989212</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.5799999999999996</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.04162902757525444</v>
+        <v>0.04120507091283798</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.16</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.04505695030093193</v>
+        <v>0.04381179809570312</v>
       </c>
       <c r="JB5" t="n">
         <v>0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.04745703563094139</v>
+        <v>0.04656153172254562</v>
       </c>
       <c r="JB6" t="n">
         <v>0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.04942620918154716</v>
+        <v>0.0478779599070549</v>
       </c>
       <c r="JB7" t="n">
         <v>0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.03486614301800728</v>
+        <v>0.03279385715723038</v>
       </c>
       <c r="JB8" t="n">
         <v>0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.01855827122926712</v>
+        <v>0.01646817848086357</v>
       </c>
       <c r="JB9" t="n">
         <v>0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.02233317866921425</v>
+        <v>0.02004436776041985</v>
       </c>
       <c r="JB10" t="n">
         <v>0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.01893867924809456</v>
+        <v>0.01674450933933258</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.3</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.01991397142410278</v>
+        <v>0.01769415661692619</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.3</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.01978090405464172</v>
+        <v>0.01754550263285637</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.3</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.01609185710549355</v>
+        <v>0.01392975449562073</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.16</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.02158470451831818</v>
+        <v>0.01948198676109314</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.02000000000000007</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0581112913787365</v>
+        <v>0.05598831921815872</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.16</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.03345482051372528</v>
+        <v>0.0313076376914978</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.007433459162712097</v>
+        <v>0.00558767095208168</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.008193608373403549</v>
+        <v>0.006075304001569748</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.01120477914810181</v>
+        <v>0.009114868938922882</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0102761834859848</v>
+        <v>0.00827152281999588</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.01146946474909782</v>
+        <v>0.009404435753822327</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.3</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.01238514110445976</v>
+        <v>0.01032470911741257</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.01365263760089874</v>
+        <v>0.01154588162899017</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.01807137206196785</v>
+        <v>0.01584131643176079</v>
       </c>
       <c r="JB25" t="n">
         <v>0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.01877370476722717</v>
+        <v>0.01662052795290947</v>
       </c>
       <c r="JB26" t="n">
         <v>0.5799999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.01339970901608467</v>
+        <v>0.01141015440225601</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.01443076878786087</v>
+        <v>0.01235963404178619</v>
       </c>
       <c r="JB28" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0145423598587513</v>
+        <v>0.01247850805521011</v>
       </c>
       <c r="JB29" t="n">
         <v>0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.01735229417681694</v>
+        <v>0.01518002897500992</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.03710253164172173</v>
+        <v>0.03511133044958115</v>
       </c>
       <c r="JB31" t="n">
         <v>0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0943184494972229</v>
+        <v>0.09284958988428116</v>
       </c>
       <c r="JB32" t="n">
         <v>0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.05377599969506264</v>
+        <v>0.05179556459188461</v>
       </c>
       <c r="JB33" t="n">
         <v>0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.02886604890227318</v>
+        <v>0.02681677415966988</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.02165120840072632</v>
+        <v>0.01949844509363174</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.02096755057573318</v>
+        <v>0.01879080012440681</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.02378822863101959</v>
+        <v>0.02155781164765358</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.01362145319581032</v>
+        <v>0.01162728667259216</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.01371388509869576</v>
+        <v>0.01162376254796982</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.04040211066603661</v>
+        <v>0.03817500919103622</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.05428392067551613</v>
+        <v>0.05215411633253098</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.05079007521271706</v>
+        <v>0.04912210255861282</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.1087712645530701</v>
+        <v>0.107879064977169</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.08984789252281189</v>
+        <v>0.08857665210962296</v>
       </c>
       <c r="JB44" t="n">
         <v>0.4399999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.01665005460381508</v>
+        <v>0.01538510248064995</v>
       </c>
       <c r="JB45" t="n">
         <v>0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.002765312790870667</v>
+        <v>0.001629838719964027</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.02655012160539627</v>
+        <v>0.0257079117000103</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.8599999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0174997765570879</v>
+        <v>-0.01777308434247971</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.008960533887147903</v>
+        <v>-0.008906930685043335</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.8599999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.01854705810546875</v>
+        <v>-0.01814554259181023</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.01891398802399635</v>
+        <v>-0.01838097348809242</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.03107882291078568</v>
+        <v>-0.03066038899123669</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.01529546175152063</v>
+        <v>-0.01500032842159271</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.03105530142784119</v>
+        <v>-0.03080207854509354</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.01801592670381069</v>
+        <v>-0.01794409938156605</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0302362497895956</v>
+        <v>-0.03034144081175327</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0233248844742775</v>
+        <v>-0.02390917576849461</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.2599999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.01194847002625465</v>
+        <v>0.01082994788885117</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.2599999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.01881054788827896</v>
+        <v>0.01737558469176292</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.2599999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.1827272474765778</v>
+        <v>-0.1872993409633636</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.2599999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.053975909948349</v>
+        <v>-0.05516673624515533</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.2599999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.04847016185522079</v>
+        <v>-0.04989440739154816</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.3999999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.1073919832706451</v>
+        <v>-0.1119904294610023</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.1199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.04729883745312691</v>
+        <v>-0.04973297193646431</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.1199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.03915832564234734</v>
+        <v>0.01156743615865707</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.1199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.1650967001914978</v>
+        <v>-0.1697104573249817</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.1199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.1216093003749847</v>
+        <v>-0.126074954867363</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.1199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.05516818910837173</v>
+        <v>-0.05888960510492325</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.2599999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.06412202119827271</v>
+        <v>-0.06816015392541885</v>
       </c>
       <c r="JB69" t="n">
         <v>0.02000000000000007</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.02081144228577614</v>
+        <v>-0.02427094429731369</v>
       </c>
       <c r="JB70" t="n">
         <v>0.3</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.001222426071763039</v>
+        <v>-0.00437324121594429</v>
       </c>
       <c r="JB71" t="n">
         <v>0.4399999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.01230823993682861</v>
+        <v>0.009662047028541565</v>
       </c>
       <c r="JB72" t="n">
         <v>0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.0295029878616333</v>
+        <v>-0.03303476795554161</v>
       </c>
       <c r="JB73" t="n">
         <v>0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.02844896167516708</v>
+        <v>-0.03213457018136978</v>
       </c>
       <c r="JB74" t="n">
         <v>0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.0242574792355299</v>
+        <v>-0.02741498313844204</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.001329738646745682</v>
+        <v>-0.00201764889061451</v>
       </c>
       <c r="JB76" t="n">
         <v>0.8599999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.04324937984347343</v>
+        <v>0.04149271547794342</v>
       </c>
       <c r="JB77" t="n">
         <v>0.5799999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003571359440684319</v>
+        <v>-0.006800852715969086</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.04930078610777855</v>
+        <v>-0.05301622301340103</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.07249122112989426</v>
+        <v>-0.07615503668785095</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.5799999999999998</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.1613975018262863</v>
+        <v>-0.1662784516811371</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0.3187664562904222</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.02064279839396477</v>
+        <v>-0.02445908635854721</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0.3187665665358978</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.003574509173631668</v>
+        <v>-0.005967669188976288</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0.3187666400328814</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.05989629775285721</v>
+        <v>-0.06330420076847076</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
         <v>0.3187668237753405</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.06548794358968735</v>
+        <v>-0.06984530389308929</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0.318768367211997</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.0782000869512558</v>
+        <v>0.07666832953691483</v>
       </c>
       <c r="JB86" t="n">
         <v>0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.04803705587983131</v>
+        <v>0.046305812895298</v>
       </c>
       <c r="JB87" t="n">
         <v>0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.0493554063141346</v>
+        <v>0.04169204831123352</v>
       </c>
       <c r="JB88" t="n">
         <v>0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.1342747360467911</v>
+        <v>-0.1382550150156021</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.1668742746114731</v>
+        <v>-0.1713983416557312</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>0.3187698371516701</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.1246128529310226</v>
+        <v>-0.1290866732597351</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.03340354561805725</v>
+        <v>-0.037276491522789</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.0190462488681078</v>
+        <v>-0.02249542810022831</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.02656613290309906</v>
+        <v>-0.03009438514709473</v>
       </c>
       <c r="JB94" t="n">
         <v>0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.0183498952537775</v>
+        <v>-0.02184895612299442</v>
       </c>
       <c r="JB95" t="n">
         <v>0.8599999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.02306080982089043</v>
+        <v>0.02040944248437881</v>
       </c>
       <c r="JB96" t="n">
         <v>0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.01138744130730629</v>
+        <v>0.008818749338388443</v>
       </c>
       <c r="JB97" t="n">
         <v>0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.001458439975976944</v>
+        <v>-0.001311954110860825</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.03451543301343918</v>
+        <v>-0.03774977475404739</v>
       </c>
       <c r="JB99" t="n">
         <v>0.16</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.1470412611961365</v>
+        <v>-0.1517447531223297</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.1570199429988861</v>
+        <v>-0.1617779731750488</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.05175910890102386</v>
+        <v>-0.05568141862750053</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.01836398802697659</v>
+        <v>-0.02189029194414616</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.01135395839810371</v>
+        <v>-0.01454800926148891</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.02000000000000007</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.02110322192311287</v>
+        <v>-0.02445716038346291</v>
       </c>
       <c r="JB105" t="n">
         <v>0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.03274764120578766</v>
+        <v>-0.03621676564216614</v>
       </c>
       <c r="JB106" t="n">
         <v>0.4399999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.07959772646427155</v>
+        <v>-0.08374372124671936</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.06955255568027496</v>
+        <v>-0.07376772165298462</v>
       </c>
       <c r="JB108" t="n">
         <v>0.02000000000000007</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.03745122626423836</v>
+        <v>-0.04091276973485947</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0.3187670075177997</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.06809353828430176</v>
+        <v>-0.07223200798034668</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0.318767154511767</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.04410015791654587</v>
+        <v>-0.04717842489480972</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0.3187670810147833</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.1411798596382141</v>
+        <v>-0.1459875702857971</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0.318767154511767</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.05183438956737518</v>
+        <v>-0.05527757108211517</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0.3187671912602589</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.08213810622692108</v>
+        <v>-0.08650456368923187</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.01046323776245117</v>
+        <v>0.007597588002681732</v>
       </c>
       <c r="JB115" t="n">
         <v>0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.01544813439249992</v>
+        <v>0.01273461431264877</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.03413337096571922</v>
+        <v>0.03221993148326874</v>
       </c>
       <c r="JB117" t="n">
         <v>0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.01688258722424507</v>
+        <v>0.01452569290995598</v>
       </c>
       <c r="JB118" t="n">
         <v>0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.03928621485829353</v>
+        <v>0.03714122623205185</v>
       </c>
       <c r="JB119" t="n">
         <v>0.8599999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.02885832265019417</v>
+        <v>0.02713081240653992</v>
       </c>
       <c r="JB120" t="n">
         <v>0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.00938604399561882</v>
+        <v>0.00653541088104248</v>
       </c>
       <c r="JB121" t="n">
         <v>0.5799999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.03358450531959534</v>
+        <v>0.03145776689052582</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.01468846574425697</v>
+        <v>0.0123823955655098</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.04859092831611633</v>
+        <v>-0.05174510926008224</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.1234141886234283</v>
+        <v>-0.1279895007610321</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.9299999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.04557560384273529</v>
+        <v>-0.04961531236767769</v>
       </c>
       <c r="JB126" t="n">
         <v>-1.14</v>
